--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484088_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484088_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9453</v>
+        <v>5.2157</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9998</v>
+        <v>5.1018</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0544</v>
+        <v>0.1139</v>
       </c>
       <c r="G2" t="n">
         <v>5.3748</v>
@@ -610,13 +610,13 @@
         <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1599</v>
+        <v>0.1105</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1928</v>
+        <v>0.2948</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3526</v>
+        <v>-0.1843</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0713</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2465</v>
+        <v>4.374</v>
       </c>
       <c r="E3" t="n">
-        <v>3.467</v>
+        <v>3.8751</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7795</v>
+        <v>0.4989</v>
       </c>
       <c r="G3" t="n">
         <v>4.8526</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3402</v>
+        <v>-0.2126</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2833</v>
+        <v>0.0027</v>
       </c>
       <c r="V3" t="n">
         <v>-0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7885</v>
+        <v>4.2973</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3483</v>
+        <v>3.7168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4402</v>
+        <v>0.5805</v>
       </c>
       <c r="G4" t="n">
         <v>1.3894</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.4435</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5384</v>
+        <v>-0.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4732</v>
+        <v>0.6135</v>
       </c>
       <c r="V4" t="n">
         <v>1.4724</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7949</v>
+        <v>3.5164</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2116</v>
+        <v>2.125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5833</v>
+        <v>1.3914</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1121</v>
+        <v>3.7616</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1588</v>
+        <v>3.1552</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0467</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0188</v>
+        <v>2.8505</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4113</v>
+        <v>2.8078</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6075</v>
+        <v>0.0427</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9067</v>
+        <v>0.9111</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2525</v>
+        <v>0.3474</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6542</v>
+        <v>0.5637</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8893</v>
+        <v>0.35</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1928</v>
+        <v>0.2664</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6965</v>
+        <v>0.0835</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7895</v>
+        <v>2.5077</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8189</v>
+        <v>2.3884</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9706</v>
+        <v>0.1194</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7616</v>
+        <v>1.5861</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1552</v>
+        <v>-1.3909</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6064000000000001</v>
+        <v>2.9771</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8505</v>
+        <v>3.3584</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8078</v>
+        <v>-0.2664</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0427</v>
+        <v>3.6248</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9111</v>
+        <v>-1.7723</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3474</v>
+        <v>-1.1246</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5637</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P6" t="n">
         <v>-0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-2.1822</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3769</v>
+        <v>-0.0269</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0396</v>
+        <v>0.0057</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3373</v>
+        <v>-0.0327</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5437</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3051</v>
+        <v>2.3548</v>
       </c>
       <c r="E7" t="n">
-        <v>2.326</v>
+        <v>1.9679</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0209</v>
+        <v>0.3869</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5861</v>
+        <v>1.1121</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3909</v>
+        <v>1.1588</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9771</v>
+        <v>-0.0467</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3584</v>
+        <v>2.0188</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2664</v>
+        <v>1.4113</v>
       </c>
       <c r="L7" t="n">
-        <v>3.6248</v>
+        <v>0.6075</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7723</v>
+        <v>-0.9067</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1246</v>
+        <v>-0.2525</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6542</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1822</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2296</v>
+        <v>0.4492</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0566</v>
+        <v>-0.051</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.173</v>
+        <v>0.5001</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5437</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2294</v>
+        <v>1.9458</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8896</v>
+        <v>1.1159</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6602</v>
+        <v>0.8299</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5148</v>
+        <v>-0.6531</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4642</v>
+        <v>-0.0507</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0506</v>
+        <v>-0.6024</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1446</v>
+        <v>-0.3675</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9839</v>
+        <v>0.2674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1606</v>
+        <v>-0.6349</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6298</v>
+        <v>-0.2856</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.3181</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.11</v>
+        <v>0.0325</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9919</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5838</v>
+        <v>0.7892</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7369</v>
+        <v>0.2608</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1531</v>
+        <v>0.5284</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.8692</v>
+        <v>1.8097</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4129</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8692</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.7833</v>
+        <v>1.8941</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3176</v>
+        <v>2.1759</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5343</v>
+        <v>-0.2818</v>
       </c>
       <c r="G9" t="n">
         <v>1.4214</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7748</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4025</v>
+        <v>0.2608</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3723</v>
+        <v>0.6248</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2065</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7544</v>
+        <v>1.5152</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5037</v>
+        <v>2.1754</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2507</v>
+        <v>-0.6602</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6531</v>
+        <v>2.5148</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0507</v>
+        <v>2.4642</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6024</v>
+        <v>0.0506</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3675</v>
+        <v>3.1446</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2674</v>
+        <v>2.9839</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6349</v>
+        <v>0.1606</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2856</v>
+        <v>-0.6298</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3181</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0325</v>
+        <v>-0.11</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5979</v>
+        <v>-0.1304</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3514</v>
+        <v>0.0227</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9493</v>
+        <v>-0.1531</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8097</v>
+        <v>-0.8692</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6032</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6359</v>
+        <v>0.0197</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3156</v>
+        <v>-0.1322</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3203</v>
+        <v>0.152</v>
       </c>
       <c r="G11" t="n">
         <v>0.657</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1097</v>
+        <v>1.4935</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0827</v>
+        <v>0.6349</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0269</v>
+        <v>0.8586</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9405</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2012</v>
+        <v>-0.2573</v>
       </c>
       <c r="E12" t="n">
         <v>-0.6821</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4808</v>
+        <v>0.4247</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4132</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.212</v>
+        <v>0.1559</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2743</v>
+        <v>0.2182</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>27.0716</v>
+        <v>27.3834</v>
       </c>
       <c r="E13" t="n">
-        <v>23.516</v>
+        <v>23.8279</v>
       </c>
       <c r="F13" t="n">
         <v>3.5556</v>
@@ -1438,7 +1438,7 @@
         <v>12.826</v>
       </c>
       <c r="I13" t="n">
-        <v>8.777600000000003</v>
+        <v>8.777600000000001</v>
       </c>
       <c r="J13" t="n">
         <v>27.213</v>
@@ -1465,19 +1465,19 @@
         <v>-9.9191</v>
       </c>
       <c r="R13" t="n">
-        <v>9.9191</v>
+        <v>9.919099999999998</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9957</v>
+        <v>4.3075</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9358999999999997</v>
+        <v>1.2475</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0598</v>
+        <v>3.0597</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4723</v>
+        <v>1.472300000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.2865</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>T. SARTOR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0135</v>
+        <v>1.4206</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8777</v>
+        <v>3.5067</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8642</v>
+        <v>-2.0861</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9713000000000001</v>
+        <v>-1.3046</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0834</v>
+        <v>-1.1439</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0547</v>
+        <v>-0.1606</v>
       </c>
       <c r="J14" t="n">
-        <v>4.686</v>
+        <v>1.8102</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5885</v>
+        <v>0.5199</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0975</v>
+        <v>1.2903</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7147</v>
+        <v>-3.1148</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6719</v>
+        <v>-1.6638</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0428</v>
+        <v>-1.4509</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1741</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S14" t="n">
-        <v>1.76</v>
+        <v>-0.4732</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4966</v>
+        <v>-0.1132</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2635</v>
+        <v>-0.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8692</v>
+        <v>1.8097</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8692</v>
+        <v>1.8097</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SARTOR</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7624</v>
+        <v>0.7849</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4249</v>
+        <v>2.6533</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.6625</v>
+        <v>-1.8684</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.3046</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1439</v>
+        <v>-1.0834</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1606</v>
+        <v>2.0547</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8102</v>
+        <v>4.686</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5199</v>
+        <v>1.5885</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2903</v>
+        <v>3.0975</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.1148</v>
+        <v>-3.7147</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6638</v>
+        <v>-2.6719</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4509</v>
+        <v>-1.0428</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3887</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.1741</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3887</v>
+        <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1314</v>
+        <v>0.5314</v>
       </c>
       <c r="T15" t="n">
-        <v>0.805</v>
+        <v>0.2722</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9364</v>
+        <v>0.2592</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8097</v>
+        <v>0.8692</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8097</v>
+        <v>0.8692</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3521</v>
+        <v>0.1957</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9778</v>
+        <v>1.7738</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6257</v>
+        <v>-1.5781</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2375</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1848</v>
+        <v>0.0284</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1189</v>
+        <v>-0.323</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3037</v>
+        <v>0.3514</v>
       </c>
       <c r="V16" t="n">
         <v>1.2065</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.3555</v>
+        <v>-2.2851</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5551</v>
+        <v>0.1591</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8004</v>
+        <v>-2.4442</v>
       </c>
       <c r="G17" t="n">
         <v>-1.7226</v>
@@ -1780,13 +1780,13 @@
         <v>0.9919</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4346</v>
+        <v>-0.3641</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3602</v>
+        <v>-0.646</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0743</v>
+        <v>0.2819</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.6136</v>
+        <v>-4.0295</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.1076</v>
+        <v>-1.9035</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.506</v>
+        <v>-2.1259</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1471</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0616</v>
+        <v>-0.4775</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6177</v>
+        <v>-0.4136</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4439</v>
+        <v>-0.0639</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.806</v>
+        <v>-4.7405</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.034</v>
+        <v>-2.932</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7721</v>
+        <v>-1.8086</v>
       </c>
       <c r="G19" t="n">
         <v>-4.9918</v>
@@ -1936,13 +1936,13 @@
         <v>0.5952</v>
       </c>
       <c r="S19" t="n">
-        <v>0.055</v>
+        <v>0.1205</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5044</v>
+        <v>-0.4023</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5594</v>
+        <v>0.5228</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2186</v>
+        <v>-4.8742</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.273</v>
+        <v>-2.0689</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9456</v>
+        <v>-2.8053</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6069</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.802</v>
+        <v>-0.4577</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8615</v>
+        <v>-0.6574</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0595</v>
+        <v>0.1997</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8097</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.7473</v>
+        <v>-5.193</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7863</v>
+        <v>-1.4802</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9611</v>
+        <v>-3.7128</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6687</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2175</v>
+        <v>-0.6631</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9238</v>
+        <v>-0.6177</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2937</v>
+        <v>-0.0454</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4724</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4586</v>
+        <v>-6.31</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.08</v>
+        <v>-3.2638</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3786</v>
+        <v>-3.0462</v>
       </c>
       <c r="G22" t="n">
         <v>-6.8957</v>
@@ -2170,13 +2170,13 @@
         <v>1.3887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3484</v>
+        <v>-0.1997</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9748</v>
+        <v>-0.1586</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3736</v>
+        <v>-0.0412</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6032</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-27.0716</v>
+        <v>-25.0311</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5556</v>
+        <v>-3.555499999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-23.5162</v>
+        <v>-21.4756</v>
       </c>
       <c r="G23" t="n">
         <v>-21.6036</v>
@@ -2248,13 +2248,13 @@
         <v>9.9194</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.9957</v>
+        <v>-1.955</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0597</v>
+        <v>-3.0596</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9358</v>
+        <v>1.1045</v>
       </c>
       <c r="V23" t="n">
         <v>-1.4724</v>
